--- a/week6/day1/Daily Challenge Dino File.xlsx
+++ b/week6/day1/Daily Challenge Dino File.xlsx
@@ -1,32 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ae89a76e0b509e53/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABFA9C0A-BA2E-42B8-8E6E-27FA0E41AD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{ABFA9C0A-BA2E-42B8-8E6E-27FA0E41AD15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69880536-3D84-4E1D-8C26-60D5D9239C57}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-9660" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-9660" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Part 2 PIVOT" sheetId="5" r:id="rId2"/>
-    <sheet name="Part 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Part 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Part 2" sheetId="3" r:id="rId2"/>
+    <sheet name="Part 3" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Part 1'!$A$1:$K$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part 2'!$A$1:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Part 3'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Part 2'!$A$1:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Part 3'!$A$1:$K$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="82" r:id="rId5"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="112">
   <si>
     <t>Name</t>
   </si>
@@ -380,21 +376,6 @@
   </si>
   <si>
     <t>Diet</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of Length (m)</t>
-  </si>
-  <si>
-    <t>top 50%</t>
-  </si>
-  <si>
-    <t>Top 50%</t>
   </si>
 </sst>
 </file>
@@ -441,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -462,11 +443,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,603 +469,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Florencia Ogorinsky" refreshedDate="45733.430818055553" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="28" xr:uid="{9342BA2A-1022-4992-BAD5-53C617F29C44}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L29" sheet="Part 2"/>
-  </cacheSource>
-  <cacheFields count="12">
-    <cacheField name="Name" numFmtId="0">
-      <sharedItems count="28">
-        <s v="Albertosaurus"/>
-        <s v="Diplodocus"/>
-        <s v="Baryonyx"/>
-        <s v="Coelophysis"/>
-        <s v="Camarasaurus"/>
-        <s v="Deinonychus"/>
-        <s v="Dromaeosaurus"/>
-        <s v="Gallimimus"/>
-        <s v="Hypsilophodon"/>
-        <s v="Orodromeus"/>
-        <s v="Oviraptor"/>
-        <s v="Pachycephalosaurus"/>
-        <s v="Troodon"/>
-        <s v="Tyrannosaurus"/>
-        <s v="Edmontosaurus"/>
-        <s v="Iguanodon"/>
-        <s v="Maiasaura"/>
-        <s v="Massospondylus"/>
-        <s v="Parasaurolophus"/>
-        <s v="Psittacosaurus"/>
-        <s v="Allosaurus"/>
-        <s v="Centrosaurus"/>
-        <s v="Chasmosaurus"/>
-        <s v="Tuojiangosaurus"/>
-        <s v="Euoplocephalus"/>
-        <s v="Tenontosaurus"/>
-        <s v="Triceratops"/>
-        <s v="Compsognathus"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Meaning of Name" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Pronunciation" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Period" numFmtId="0">
-      <sharedItems count="3">
-        <s v="Cretaceous"/>
-        <s v="Jurassic"/>
-        <s v="Triassic"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Diet" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Length (m)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1" maxValue="26"/>
-    </cacheField>
-    <cacheField name="top 50%" numFmtId="0">
-      <sharedItems count="2">
-        <s v="Top 50%"/>
-        <s v="Rest"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Height  (m)" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.7" maxValue="9"/>
-    </cacheField>
-    <cacheField name="Mass kg" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.6" maxValue="20000"/>
-    </cacheField>
-    <cacheField name="No. of feet it walked on?" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
-    </cacheField>
-    <cacheField name="Hip Type" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Group" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="28">
-  <r>
-    <x v="0"/>
-    <s v="Alberta lizard"/>
-    <s v="al-BERT-oh-saw-russ"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="9"/>
-    <x v="0"/>
-    <n v="3.5"/>
-    <n v="1500"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <s v="double beam"/>
-    <s v="dip-lod-OH-kuss"/>
-    <x v="1"/>
-    <s v="herbivore"/>
-    <n v="26"/>
-    <x v="0"/>
-    <n v="8"/>
-    <n v="10000"/>
-    <n v="4"/>
-    <s v="lizard"/>
-    <s v="sauropod"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <s v="heavy claw"/>
-    <s v="bah-ree-ON-icks"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="10"/>
-    <x v="0"/>
-    <n v="4"/>
-    <n v="2000"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <s v="hollow form"/>
-    <s v="see-LOH-fiss-iss"/>
-    <x v="2"/>
-    <s v="carnivore"/>
-    <n v="3"/>
-    <x v="1"/>
-    <n v="2"/>
-    <n v="27"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <s v="chambered lizard"/>
-    <s v="KAM-ar-a-saw-russ"/>
-    <x v="1"/>
-    <s v="herbivore"/>
-    <n v="18"/>
-    <x v="0"/>
-    <n v="9"/>
-    <n v="20000"/>
-    <n v="4"/>
-    <s v="lizard"/>
-    <s v="sauropod"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <s v="terrible claw"/>
-    <s v="die-NON-i-kuss"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="3"/>
-    <x v="1"/>
-    <n v="1.5"/>
-    <n v="75"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <s v="running lizard"/>
-    <s v="DROM-ee-oh-saw-russ"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="1.8"/>
-    <x v="1"/>
-    <n v="0.8"/>
-    <n v="15"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <s v="fowl mimic"/>
-    <s v="gal-i-ME-muss"/>
-    <x v="0"/>
-    <s v="omnivore"/>
-    <n v="5.6"/>
-    <x v="1"/>
-    <n v="3"/>
-    <n v="200"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <s v="high-ridge tooth"/>
-    <s v="hip-sill-OH-fo-don"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="2"/>
-    <x v="1"/>
-    <n v="0.8"/>
-    <n v="50"/>
-    <n v="2"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <s v="mountain runner"/>
-    <s v="or-odd-rom-AY-us"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="2.5"/>
-    <x v="1"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="2"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="10"/>
-    <s v="egg thief"/>
-    <s v="o-vee-RAP-tor"/>
-    <x v="0"/>
-    <s v="omnivore"/>
-    <n v="1.8"/>
-    <x v="1"/>
-    <n v="0.8"/>
-    <n v="20"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="11"/>
-    <s v="thick-headed lizard"/>
-    <s v="pack-i-KEF-al-oh-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="8"/>
-    <x v="0"/>
-    <n v="6"/>
-    <n v="3000"/>
-    <n v="2"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <s v="wounding tooth"/>
-    <s v="TRO-o-don"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="2"/>
-    <x v="1"/>
-    <n v="1.3"/>
-    <n v="40"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="13"/>
-    <s v="tyrant lizard"/>
-    <s v="tie-RAN-oh-saw-russ"/>
-    <x v="0"/>
-    <s v="carnivore"/>
-    <n v="12"/>
-    <x v="0"/>
-    <n v="5.6"/>
-    <n v="7000"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="14"/>
-    <s v="Edmonton lizard"/>
-    <s v="ed-MON-toe-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="13"/>
-    <x v="0"/>
-    <n v="3.5"/>
-    <n v="3400"/>
-    <s v="2 or 4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <s v="iguana tooth"/>
-    <s v="ig-WAN-oh-don"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="10"/>
-    <x v="0"/>
-    <n v="5"/>
-    <n v="4500"/>
-    <s v="2 or 4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <s v="good mother lizard"/>
-    <s v="my-ah-SAW-rah"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="9"/>
-    <x v="0"/>
-    <n v="2.2999999999999998"/>
-    <n v="2500"/>
-    <s v="2 or 4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="17"/>
-    <s v="massive vertebrae"/>
-    <s v="mass-oh-SPON-di-luss"/>
-    <x v="2"/>
-    <s v="herbivore"/>
-    <n v="4"/>
-    <x v="1"/>
-    <n v="1"/>
-    <n v="70"/>
-    <s v="2 or 4"/>
-    <s v="lizard"/>
-    <s v="prosauropod"/>
-  </r>
-  <r>
-    <x v="18"/>
-    <s v="like 'Saurolophus' - the ridged lizard"/>
-    <s v="pa-ra-saw-ROL-off-us"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="10"/>
-    <x v="0"/>
-    <n v="5.2"/>
-    <n v="3500"/>
-    <s v="2 or 4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <s v="parrot lizard"/>
-    <s v="SIT-a-co-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="2.5"/>
-    <x v="1"/>
-    <n v="1"/>
-    <n v="50"/>
-    <s v="2 or 4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="20"/>
-    <s v="different reptile"/>
-    <s v="AL-oh-saw-russ"/>
-    <x v="1"/>
-    <s v="carnivore"/>
-    <n v="12"/>
-    <x v="0"/>
-    <n v="5"/>
-    <n v="2000"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-  <r>
-    <x v="21"/>
-    <s v="horned lizard"/>
-    <s v="CEN-tro-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="6"/>
-    <x v="1"/>
-    <n v="2"/>
-    <n v="1000"/>
-    <n v="4"/>
-    <s v="bird"/>
-    <s v="ceratopian"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <s v="ravine reptile"/>
-    <s v="KAZ-mo-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="5.2"/>
-    <x v="1"/>
-    <n v="3.6"/>
-    <n v="2500"/>
-    <n v="4"/>
-    <s v="bird"/>
-    <s v="ceratopian"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <s v="Tuijiang lizard"/>
-    <s v="too-WANG-oh-saw-russ"/>
-    <x v="1"/>
-    <s v="herbivore"/>
-    <n v="7"/>
-    <x v="0"/>
-    <n v="2"/>
-    <n v="1500"/>
-    <s v="on 4 legs"/>
-    <s v="bird"/>
-    <s v="stegosaur"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <s v="well-armoured head"/>
-    <s v="you-OH-plo-kef-ah-luss"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="6"/>
-    <x v="1"/>
-    <n v="1.8"/>
-    <n v="2000"/>
-    <n v="4"/>
-    <s v="bird"/>
-    <s v="ankylosaur"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <s v="sinew lizard"/>
-    <s v="ten-ON-toe-saw-russ"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="7.3"/>
-    <x v="0"/>
-    <n v="2.5"/>
-    <n v="900"/>
-    <n v="4"/>
-    <s v="bird"/>
-    <s v="ornithopod"/>
-  </r>
-  <r>
-    <x v="26"/>
-    <s v="three-horned face"/>
-    <s v="tri-SER-a-tops"/>
-    <x v="0"/>
-    <s v="herbivore"/>
-    <n v="9"/>
-    <x v="0"/>
-    <n v="3"/>
-    <n v="5500"/>
-    <n v="4"/>
-    <s v="bird"/>
-    <s v="ceratopian"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <s v="pretty jaw"/>
-    <s v="comp-so-g-NATH-us"/>
-    <x v="1"/>
-    <s v="carnivore"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="0.7"/>
-    <n v="3.6"/>
-    <n v="2"/>
-    <s v="lizard"/>
-    <s v="theropod"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70FEF3BF-3DFB-4186-B3BB-AA59D96B1206}" name="PivotTable7" cacheId="82" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="12">
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="29">
-        <item x="0"/>
-        <item x="20"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="3"/>
-        <item x="27"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="23"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="3">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="3" hier="-1"/>
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Length (m)" fld="5" baseField="0" baseItem="9"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2443,180 +1822,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4546C54B-F921-45E6-A7B3-AE8B475A598A}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="26" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="34.77734375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="27" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="37.88671875" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="29" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="19.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="10">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="10">
-        <v>63</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2" filterMode="1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.109375" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2636,25 +1859,22 @@
         <v>107</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="I1" s="7" t="s">
         <v>109</v>
       </c>
+      <c r="I1" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="J1" s="6" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -2673,27 +1893,23 @@
       <c r="F2" s="4">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="str">
-        <f>IF(F2&gt;=_xlfn.PERCENTILE.INC($F$2:$F$29, 0.5), "Top 50%", "Rest")</f>
-        <v>Top 50%</v>
+      <c r="G2" s="4">
+        <v>3.5</v>
       </c>
       <c r="H2" s="4">
-        <v>3.5</v>
+        <v>1500</v>
       </c>
       <c r="I2" s="4">
-        <v>1500</v>
-      </c>
-      <c r="J2" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -2712,27 +1928,23 @@
       <c r="F3" s="4">
         <v>26</v>
       </c>
-      <c r="G3" s="4" t="str">
-        <f>IF(F3&gt;=_xlfn.PERCENTILE.INC($F$2:$F$29, 0.5), "Top 50%", "Rest")</f>
-        <v>Top 50%</v>
+      <c r="G3" s="4">
+        <v>8</v>
       </c>
       <c r="H3" s="4">
-        <v>8</v>
+        <v>10000</v>
       </c>
       <c r="I3" s="4">
-        <v>10000</v>
-      </c>
-      <c r="J3" s="4">
         <v>4</v>
       </c>
+      <c r="J3" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="K3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -2751,27 +1963,23 @@
       <c r="F4" s="4">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="str">
-        <f t="shared" ref="G4:G29" si="0">IF(F4&gt;=_xlfn.PERCENTILE.INC($F$2:$F$29, 0.5), "Top 50%", "Rest")</f>
-        <v>Top 50%</v>
+      <c r="G4" s="4">
+        <v>4</v>
       </c>
       <c r="H4" s="4">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="I4" s="4">
-        <v>2000</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -2790,27 +1998,23 @@
       <c r="F5" s="4">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G5" s="4">
+        <v>2</v>
       </c>
       <c r="H5" s="4">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4">
-        <v>27</v>
-      </c>
-      <c r="J5" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -2829,27 +2033,23 @@
       <c r="F6" s="4">
         <v>18</v>
       </c>
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G6" s="4">
+        <v>9</v>
       </c>
       <c r="H6" s="4">
-        <v>9</v>
+        <v>20000</v>
       </c>
       <c r="I6" s="4">
-        <v>20000</v>
-      </c>
-      <c r="J6" s="4">
         <v>4</v>
       </c>
+      <c r="J6" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -2868,27 +2068,23 @@
       <c r="F7" s="4">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G7" s="4">
+        <v>1.5</v>
       </c>
       <c r="H7" s="4">
-        <v>1.5</v>
+        <v>75</v>
       </c>
       <c r="I7" s="4">
-        <v>75</v>
-      </c>
-      <c r="J7" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2907,27 +2103,23 @@
       <c r="F8" s="4">
         <v>1.8</v>
       </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G8" s="4">
+        <v>0.8</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="I8" s="4">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
@@ -2946,27 +2138,23 @@
       <c r="F9" s="4">
         <v>5.6</v>
       </c>
-      <c r="G9" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G9" s="4">
+        <v>3</v>
       </c>
       <c r="H9" s="4">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="I9" s="4">
-        <v>200</v>
-      </c>
-      <c r="J9" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>59</v>
       </c>
@@ -2985,27 +2173,23 @@
       <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G10" s="4">
+        <v>0.8</v>
       </c>
       <c r="H10" s="4">
-        <v>0.8</v>
+        <v>50</v>
       </c>
       <c r="I10" s="4">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="4">
-        <v>2</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>72</v>
       </c>
@@ -3024,27 +2208,23 @@
       <c r="F11" s="4">
         <v>2.5</v>
       </c>
-      <c r="G11" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G11" s="4">
+        <v>1</v>
       </c>
       <c r="H11" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I11" s="4">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="4">
-        <v>2</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>75</v>
       </c>
@@ -3063,27 +2243,23 @@
       <c r="F12" s="4">
         <v>1.8</v>
       </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G12" s="4">
+        <v>0.8</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8</v>
+        <v>20</v>
       </c>
       <c r="I12" s="4">
-        <v>20</v>
-      </c>
-      <c r="J12" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
@@ -3102,27 +2278,23 @@
       <c r="F13" s="4">
         <v>8</v>
       </c>
-      <c r="G13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G13" s="4">
+        <v>6</v>
       </c>
       <c r="H13" s="4">
-        <v>6</v>
+        <v>3000</v>
       </c>
       <c r="I13" s="4">
-        <v>3000</v>
-      </c>
-      <c r="J13" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>93</v>
       </c>
@@ -3141,27 +2313,23 @@
       <c r="F14" s="4">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G14" s="4">
+        <v>1.3</v>
       </c>
       <c r="H14" s="4">
-        <v>1.3</v>
+        <v>40</v>
       </c>
       <c r="I14" s="4">
-        <v>40</v>
-      </c>
-      <c r="J14" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>100</v>
       </c>
@@ -3180,27 +2348,23 @@
       <c r="F15" s="4">
         <v>12</v>
       </c>
-      <c r="G15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G15" s="4">
+        <v>5.6</v>
       </c>
       <c r="H15" s="4">
-        <v>5.6</v>
+        <v>7000</v>
       </c>
       <c r="I15" s="4">
-        <v>7000</v>
-      </c>
-      <c r="J15" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>
@@ -3219,27 +2383,23 @@
       <c r="F16" s="4">
         <v>13</v>
       </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G16" s="4">
+        <v>3.5</v>
       </c>
       <c r="H16" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="I16" s="4">
         <v>3400</v>
       </c>
+      <c r="I16" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J16" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>62</v>
       </c>
@@ -3258,27 +2418,23 @@
       <c r="F17" s="4">
         <v>10</v>
       </c>
-      <c r="G17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G17" s="4">
+        <v>5</v>
       </c>
       <c r="H17" s="4">
-        <v>5</v>
-      </c>
-      <c r="I17" s="4">
         <v>4500</v>
       </c>
+      <c r="I17" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J17" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>65</v>
       </c>
@@ -3297,27 +2453,23 @@
       <c r="F18" s="4">
         <v>9</v>
       </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G18" s="4">
+        <v>2.2999999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="I18" s="4">
         <v>2500</v>
       </c>
+      <c r="I18" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>68</v>
       </c>
@@ -3336,27 +2488,23 @@
       <c r="F19" s="4">
         <v>4</v>
       </c>
-      <c r="G19" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G19" s="4">
+        <v>1</v>
       </c>
       <c r="H19" s="4">
-        <v>1</v>
-      </c>
-      <c r="I19" s="4">
         <v>70</v>
       </c>
+      <c r="I19" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J19" s="4" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>81</v>
       </c>
@@ -3375,27 +2523,23 @@
       <c r="F20" s="4">
         <v>10</v>
       </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G20" s="4">
+        <v>5.2</v>
       </c>
       <c r="H20" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="I20" s="4">
         <v>3500</v>
       </c>
+      <c r="I20" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J20" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>84</v>
       </c>
@@ -3414,27 +2558,23 @@
       <c r="F21" s="4">
         <v>2.5</v>
       </c>
-      <c r="G21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G21" s="4">
+        <v>1</v>
       </c>
       <c r="H21" s="4">
-        <v>1</v>
-      </c>
-      <c r="I21" s="4">
         <v>50</v>
       </c>
+      <c r="I21" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="J21" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
@@ -3453,27 +2593,23 @@
       <c r="F22" s="4">
         <v>12</v>
       </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G22" s="4">
+        <v>5</v>
       </c>
       <c r="H22" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="I22" s="4">
-        <v>2000</v>
-      </c>
-      <c r="J22" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
@@ -3492,27 +2628,23 @@
       <c r="F23" s="4">
         <v>6</v>
       </c>
-      <c r="G23" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G23" s="4">
+        <v>2</v>
       </c>
       <c r="H23" s="4">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="I23" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J23" s="4">
         <v>4</v>
       </c>
+      <c r="J23" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -3531,27 +2663,23 @@
       <c r="F24" s="4">
         <v>5.2</v>
       </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G24" s="4">
+        <v>3.6</v>
       </c>
       <c r="H24" s="4">
-        <v>3.6</v>
+        <v>2500</v>
       </c>
       <c r="I24" s="4">
-        <v>2500</v>
-      </c>
-      <c r="J24" s="4">
         <v>4</v>
       </c>
+      <c r="J24" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>96</v>
       </c>
@@ -3570,27 +2698,23 @@
       <c r="F25" s="4">
         <v>7</v>
       </c>
-      <c r="G25" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G25" s="4">
+        <v>2</v>
       </c>
       <c r="H25" s="4">
-        <v>2</v>
-      </c>
-      <c r="I25" s="4">
         <v>1500</v>
       </c>
+      <c r="I25" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="J25" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
@@ -3609,27 +2733,23 @@
       <c r="F26" s="4">
         <v>6</v>
       </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G26" s="4">
+        <v>1.8</v>
       </c>
       <c r="H26" s="4">
-        <v>1.8</v>
+        <v>2000</v>
       </c>
       <c r="I26" s="4">
-        <v>2000</v>
-      </c>
-      <c r="J26" s="4">
         <v>4</v>
       </c>
+      <c r="J26" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>87</v>
       </c>
@@ -3648,27 +2768,23 @@
       <c r="F27" s="4">
         <v>7.3</v>
       </c>
-      <c r="G27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G27" s="4">
+        <v>2.5</v>
       </c>
       <c r="H27" s="4">
-        <v>2.5</v>
+        <v>900</v>
       </c>
       <c r="I27" s="4">
-        <v>900</v>
-      </c>
-      <c r="J27" s="4">
         <v>4</v>
       </c>
+      <c r="J27" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>90</v>
       </c>
@@ -3687,27 +2803,23 @@
       <c r="F28" s="4">
         <v>9</v>
       </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Top 50%</v>
+      <c r="G28" s="4">
+        <v>3</v>
       </c>
       <c r="H28" s="4">
-        <v>3</v>
+        <v>5500</v>
       </c>
       <c r="I28" s="4">
-        <v>5500</v>
-      </c>
-      <c r="J28" s="4">
         <v>4</v>
       </c>
+      <c r="J28" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="K28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
@@ -3726,37 +2838,31 @@
       <c r="F29" s="4">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rest</v>
+      <c r="G29" s="4">
+        <v>0.7</v>
       </c>
       <c r="H29" s="4">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="I29" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="J29" s="4">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="4" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:K29" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="3">
       <filters>
         <filter val="Jurassic"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Top 50%"/>
-      </filters>
+    <filterColumn colId="5">
+      <top10 percent="1" val="50" filterVal="7"/>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="A2:A29">
@@ -3767,7 +2873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3" filterMode="1">
     <tabColor rgb="FFFF0000"/>
